--- a/docs/محصولات-سایت.xlsx
+++ b/docs/محصولات-سایت.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/code1-15-10-10.png</t>
+          <t>postal-carton-code-1.png</t>
         </is>
       </c>
       <c r="N2" s="8" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/code2-20-15-10.png</t>
+          <t>postal-carton-code-2.png</t>
         </is>
       </c>
       <c r="N3" s="8" t="inlineStr"/>
@@ -820,7 +820,7 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/i6av7NjkjZmD20AYElpQHgPp5ng-QF7D8fAfSBe2Qm2bWv0Wdw.png</t>
+          <t>postal-carton-code-3.png</t>
         </is>
       </c>
       <c r="N4" s="8" t="inlineStr"/>
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/code4-30-20-20.png</t>
+          <t>postal-carton-code-4.png</t>
         </is>
       </c>
       <c r="N5" s="8" t="inlineStr"/>
@@ -950,7 +950,7 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/code5-35-25-20.png</t>
+          <t>postal-carton-code-5.png</t>
         </is>
       </c>
       <c r="N6" s="8" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/CtjYt5F7VPpz16GUv0vAbqSvoHY-QDgCZNq4SEaeDPmi-nsMPw.png</t>
+          <t>postal-carton-code-6.png</t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/RPWi3vJzqjwg4TBpmvKKpxJFh98-DAV61LgqTqO7y8w1-r5gGg.png</t>
+          <t>postal-carton-code-7.png</t>
         </is>
       </c>
       <c r="N8" s="8" t="inlineStr"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/code8-45-40-30.png</t>
+          <t>postal-carton-code-8.png</t>
         </is>
       </c>
       <c r="N9" s="8" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/code9-55-45-35.png</t>
+          <t>postal-carton-code-9.png</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/JmcmAMhSqph-oQ2iWVAc80seHIw-8oRNhN9jTVega7j3R-RHlA.png</t>
+          <t>moving-carton-small.jpg</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr"/>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/82QBbWeLRaC2E78Egi8BNvdA9wQ-w5D1hsCMTie6CGnRqWE7Mg.png</t>
+          <t>moving-carton-medium.jpg</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr"/>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/pRruMsWQknsoOQgelVgDdZopwvA-C6ZH_oJKSH-9-hI7SlsCgA.png</t>
+          <t>moving-carton-large.jpg</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr"/>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/gWQSctIC04un6jWAszam9Kfmrxc-PNxumlQaTOCwn4V6lyb9WA.png</t>
+          <t>moving-carton-printed.jpg, moving-carton-small.jpg</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr"/>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/irYe45htNsoZnSCWW-IqXVZofpo-HX69zW58RD-CP-5Lboqzcg.png</t>
+          <t>moving-carton-printed.jpg, moving-carton-medium.jpg</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/ob-wnGvX36k9v2zoUaWCOKvbH4E-aFX07fdaSrO3jI_F61b5fg.png</t>
+          <t>moving-carton-printed.jpg, moving-carton-large.jpg</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/box-piza-2-leyer-2.jpg, https://parsiancarton.com/wp-content/uploads/2026/08/box-pizza-2-leyer.jpg</t>
+          <t>pizza-box-single.jpg, pizza-box-kraft-printed.png</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/pizzapack-with-print.png</t>
+          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr"/>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/fZ-m_k6Om4-u5S8kGY1AY-74quc-YVfM8wTxRjOhNRCmDEEw4w.jpg</t>
+          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr"/>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/pizzapack-with-print.png</t>
+          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr"/>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/IMG_2310.jpg</t>
+          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr"/>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/pizza-pack-20-34.jpg</t>
+          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/pizzapack-with-print.png</t>
+          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr"/>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/IMG_2310.jpg</t>
+          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr"/>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/pizzapack-with-print.png</t>
+          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr"/>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/fZ-m_k6Om4-u5S8kGY1AY-74quc-YVfM8wTxRjOhNRCmDEEw4w.jpg</t>
+          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/box-pizza-2-leyer.jpg, https://parsiancarton.com/wp-content/uploads/2026/08/box-pizza-2-leyer.jpg, https://parsiancarton.com/wp-content/uploads/2026/08/box-piza-2-leyer-2.jpg</t>
+          <t>pizza-box-single.jpg, pizza-box-kraft-printed.png</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr"/>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/pizza-pack-20-34-pure.png</t>
+          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/5me7tOoHDdqDTKl9UJNdlCFxaMU-2MnnnEuS2mt79tPc_FmWw.jpg</t>
+          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr"/>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/pizza-pack-20-34.jpg</t>
+          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr"/>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="M31" s="9" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/ju-01-2.svg</t>
+          <t>cup-holder-2-kraft.png, cup-holder-2-kraft-open.png</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="M34" s="9" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/ju-02-2.svg</t>
+          <t>cup-holder-2-printed.png, cup-holder-2-printed-blue.jpg, cup-holder-2-printed-colors.jpg</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr"/>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/ju-03-vip-2.svg</t>
+          <t>cup-holder-2-glued-vip.jpg</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="M44" s="9" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/ju-06-2.svg</t>
+          <t>cup-holder-4-kraft.png, cup-holder-4-kraft-top.jpg, cup-holder-4-kraft-in-use.png</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr"/>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="M47" s="9" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/ju-07-2.svg</t>
+          <t>cup-holder-4-printed.png</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr"/>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/ju-08-vip-2.svg</t>
+          <t>cup-holder-4-glued-vip.jpg</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr"/>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="M54" s="9" t="inlineStr">
         <is>
-          <t>https://parsiancarton.com/wp-content/uploads/2026/08/ju-10-2.svg</t>
+          <t>cup-holder-4-printed-cafe.png</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr"/>
@@ -3952,7 +3952,6 @@
           <t>چطور کار کنم؟</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
@@ -4011,7 +4010,6 @@
           <t>قاعده‌های مهم</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
@@ -4094,7 +4092,6 @@
           <t>نوشتن توضیحات</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -4141,7 +4138,6 @@
           <t>ستون‌ها</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">

--- a/docs/محصولات-سایت.xlsx
+++ b/docs/محصولات-سایت.xlsx
@@ -1470,7 +1470,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>moving-carton-printed.jpg, moving-carton-small.jpg</t>
+          <t>moving-carton-printed.jpg</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr"/>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>moving-carton-printed.jpg, moving-carton-medium.jpg</t>
+          <t>moving-carton-printed.jpg</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>moving-carton-printed.jpg, moving-carton-large.jpg</t>
+          <t>moving-carton-printed.jpg</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr"/>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>pizza-box-single.jpg, pizza-box-kraft-printed.png</t>
+          <t>pizza-box-single.jpg</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
+          <t>pizza-box-kraft-printed.png</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr"/>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
+          <t>pizza-box-kraft-printed.png</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr"/>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
+          <t>pizza-box-kraft-printed.png</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr"/>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
+          <t>pizza-box-kraft-printed.png</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr"/>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
+          <t>pizza-box-kraft-printed.png</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
+          <t>pizza-box-kraft-printed.png</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr"/>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
+          <t>pizza-box-kraft-printed.png</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr"/>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
+          <t>pizza-box-kraft-printed.png</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr"/>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
+          <t>pizza-box-kraft-printed.png</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr"/>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>pizza-box-single.jpg, pizza-box-kraft-printed.png</t>
+          <t>pizza-box-single.jpg</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr"/>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
+          <t>pizza-box-kraft-printed.png</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
+          <t>pizza-box-kraft-printed.png</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr"/>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>pizza-box-kraft-printed.png, pizza-box-white-printed.png</t>
+          <t>pizza-box-kraft-printed.png</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr"/>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="M31" s="9" t="inlineStr">
         <is>
-          <t>cup-holder-2-kraft.png, cup-holder-2-kraft-open.png</t>
+          <t>cup-holder-2-kraft.png</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr"/>
@@ -2521,7 +2521,11 @@
       </c>
       <c r="K32" s="12" t="inlineStr"/>
       <c r="L32" s="12" t="inlineStr"/>
-      <c r="M32" s="12" t="inlineStr"/>
+      <c r="M32" s="12" t="inlineStr">
+        <is>
+          <t>cup-holder-2-kraft.png</t>
+        </is>
+      </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
           <t>ju-01</t>
@@ -2575,7 +2579,11 @@
       </c>
       <c r="K33" s="12" t="inlineStr"/>
       <c r="L33" s="12" t="inlineStr"/>
-      <c r="M33" s="12" t="inlineStr"/>
+      <c r="M33" s="12" t="inlineStr">
+        <is>
+          <t>cup-holder-2-kraft-open.png</t>
+        </is>
+      </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
           <t>ju-01</t>
@@ -2642,7 +2650,7 @@
       </c>
       <c r="M34" s="9" t="inlineStr">
         <is>
-          <t>cup-holder-2-printed.png, cup-holder-2-printed-blue.jpg, cup-holder-2-printed-colors.jpg</t>
+          <t>cup-holder-2-printed.png</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr"/>
@@ -2694,7 +2702,11 @@
       </c>
       <c r="K35" s="12" t="inlineStr"/>
       <c r="L35" s="12" t="inlineStr"/>
-      <c r="M35" s="12" t="inlineStr"/>
+      <c r="M35" s="12" t="inlineStr">
+        <is>
+          <t>cup-holder-2-printed-blue.jpg</t>
+        </is>
+      </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
           <t>ju-02</t>
@@ -2748,7 +2760,11 @@
       </c>
       <c r="K36" s="12" t="inlineStr"/>
       <c r="L36" s="12" t="inlineStr"/>
-      <c r="M36" s="12" t="inlineStr"/>
+      <c r="M36" s="12" t="inlineStr">
+        <is>
+          <t>cup-holder-2-printed-colors.jpg</t>
+        </is>
+      </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
           <t>ju-02</t>
@@ -3219,7 +3235,7 @@
       </c>
       <c r="M44" s="9" t="inlineStr">
         <is>
-          <t>cup-holder-4-kraft.png, cup-holder-4-kraft-top.jpg, cup-holder-4-kraft-in-use.png</t>
+          <t>cup-holder-4-kraft.png</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr"/>
@@ -3271,7 +3287,11 @@
       </c>
       <c r="K45" s="12" t="inlineStr"/>
       <c r="L45" s="12" t="inlineStr"/>
-      <c r="M45" s="12" t="inlineStr"/>
+      <c r="M45" s="12" t="inlineStr">
+        <is>
+          <t>cup-holder-4-kraft-top.jpg</t>
+        </is>
+      </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
           <t>ju-06</t>
@@ -3325,7 +3345,11 @@
       </c>
       <c r="K46" s="12" t="inlineStr"/>
       <c r="L46" s="12" t="inlineStr"/>
-      <c r="M46" s="12" t="inlineStr"/>
+      <c r="M46" s="12" t="inlineStr">
+        <is>
+          <t>cup-holder-4-kraft-in-use.png</t>
+        </is>
+      </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
           <t>ju-06</t>
@@ -3444,7 +3468,11 @@
       </c>
       <c r="K48" s="12" t="inlineStr"/>
       <c r="L48" s="12" t="inlineStr"/>
-      <c r="M48" s="12" t="inlineStr"/>
+      <c r="M48" s="12" t="inlineStr">
+        <is>
+          <t>cup-holder-4-printed.png</t>
+        </is>
+      </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
           <t>ju-07</t>
@@ -3498,7 +3526,11 @@
       </c>
       <c r="K49" s="12" t="inlineStr"/>
       <c r="L49" s="12" t="inlineStr"/>
-      <c r="M49" s="12" t="inlineStr"/>
+      <c r="M49" s="12" t="inlineStr">
+        <is>
+          <t>cup-holder-4-printed.png</t>
+        </is>
+      </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
           <t>ju-07</t>
@@ -3848,7 +3880,11 @@
       </c>
       <c r="K55" s="12" t="inlineStr"/>
       <c r="L55" s="12" t="inlineStr"/>
-      <c r="M55" s="12" t="inlineStr"/>
+      <c r="M55" s="12" t="inlineStr">
+        <is>
+          <t>cup-holder-4-printed-cafe.png</t>
+        </is>
+      </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
           <t>ju-10</t>
@@ -3902,7 +3938,11 @@
       </c>
       <c r="K56" s="12" t="inlineStr"/>
       <c r="L56" s="12" t="inlineStr"/>
-      <c r="M56" s="12" t="inlineStr"/>
+      <c r="M56" s="12" t="inlineStr">
+        <is>
+          <t>cup-holder-4-printed-cafe.png</t>
+        </is>
+      </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
           <t>ju-10</t>
